--- a/exposures_meta_analysis_uterine_combined.xlsx
+++ b/exposures_meta_analysis_uterine_combined.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <si>
     <t>Exposure</t>
   </si>
@@ -128,6 +128,9 @@
   </si>
   <si>
     <t>iron</t>
+  </si>
+  <si>
+    <t>red_meat</t>
   </si>
   <si>
     <t>bcaas</t>
@@ -494,7 +497,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:K32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -1347,25 +1350,25 @@
         <v>38</v>
       </c>
       <c r="B29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C29">
-        <v>1.44</v>
+        <v>1.27</v>
       </c>
       <c r="D29">
-        <v>1.28</v>
+        <v>1.1</v>
       </c>
       <c r="E29">
-        <v>1.62</v>
+        <v>1.46</v>
       </c>
       <c r="H29">
         <v>0</v>
       </c>
       <c r="J29">
-        <v>4326</v>
+        <v>26138</v>
       </c>
       <c r="K29">
-        <v>635</v>
+        <v>561</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -1376,22 +1379,22 @@
         <v>1</v>
       </c>
       <c r="C30">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="D30">
-        <v>1.05</v>
+        <v>1.28</v>
       </c>
       <c r="E30">
-        <v>2.51</v>
+        <v>1.62</v>
       </c>
       <c r="H30">
         <v>0</v>
       </c>
       <c r="J30">
-        <v>667</v>
+        <v>4326</v>
       </c>
       <c r="K30">
-        <v>313</v>
+        <v>635</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -1402,21 +1405,47 @@
         <v>1</v>
       </c>
       <c r="C31">
+        <v>1.67</v>
+      </c>
+      <c r="D31">
+        <v>1.05</v>
+      </c>
+      <c r="E31">
+        <v>2.51</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>667</v>
+      </c>
+      <c r="K31">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32">
+        <v>1</v>
+      </c>
+      <c r="C32">
         <v>2.09</v>
       </c>
-      <c r="D31">
+      <c r="D32">
         <v>1.24</v>
       </c>
-      <c r="E31">
+      <c r="E32">
         <v>3.52</v>
       </c>
-      <c r="H31">
-        <v>0</v>
-      </c>
-      <c r="J31">
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="J32">
         <v>53487</v>
       </c>
-      <c r="K31">
+      <c r="K32">
         <v>515</v>
       </c>
     </row>

--- a/exposures_meta_analysis_uterine_combined.xlsx
+++ b/exposures_meta_analysis_uterine_combined.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
   <si>
     <t>Exposure</t>
   </si>
@@ -52,97 +52,109 @@
     <t>eggs</t>
   </si>
   <si>
+    <t>folic_acid</t>
+  </si>
+  <si>
+    <t>lutein</t>
+  </si>
+  <si>
+    <t>antioxidants</t>
+  </si>
+  <si>
+    <t>mineral_supplements</t>
+  </si>
+  <si>
+    <t>legumes</t>
+  </si>
+  <si>
+    <t>vitamin_e</t>
+  </si>
+  <si>
     <t>vitamin_c</t>
   </si>
   <si>
-    <t>folic_acid</t>
-  </si>
-  <si>
-    <t>lutein</t>
-  </si>
-  <si>
-    <t>mineral_supplements</t>
+    <t>mediterranean_diet</t>
+  </si>
+  <si>
+    <t>garlic</t>
+  </si>
+  <si>
+    <t>calcium</t>
+  </si>
+  <si>
+    <t>beta-carotene</t>
+  </si>
+  <si>
+    <t>quercetin</t>
+  </si>
+  <si>
+    <t>lycopene</t>
+  </si>
+  <si>
+    <t>olive</t>
+  </si>
+  <si>
+    <t>non-alcoholic_fermented_foods</t>
+  </si>
+  <si>
+    <t>yogurt</t>
   </si>
   <si>
     <t>vitamin_d</t>
   </si>
   <si>
-    <t>legumes</t>
-  </si>
-  <si>
-    <t>vitamin_e</t>
-  </si>
-  <si>
-    <t>mediterranean_diet</t>
-  </si>
-  <si>
-    <t>antioxidants</t>
-  </si>
-  <si>
-    <t>garlic</t>
-  </si>
-  <si>
-    <t>quercetin</t>
-  </si>
-  <si>
-    <t>beta-carotene</t>
-  </si>
-  <si>
-    <t>calcium</t>
-  </si>
-  <si>
-    <t>yogurt</t>
-  </si>
-  <si>
-    <t>olive</t>
-  </si>
-  <si>
-    <t>non-alcoholic_fermented_foods</t>
-  </si>
-  <si>
     <t>tea</t>
   </si>
   <si>
     <t>green_tea</t>
   </si>
   <si>
+    <t>vitamin_b12</t>
+  </si>
+  <si>
+    <t>fish_oil</t>
+  </si>
+  <si>
+    <t>copper</t>
+  </si>
+  <si>
+    <t>vitamin_a</t>
+  </si>
+  <si>
+    <t>caffeine</t>
+  </si>
+  <si>
+    <t>carnitine</t>
+  </si>
+  <si>
+    <t>selenium</t>
+  </si>
+  <si>
+    <t>phosphorus</t>
+  </si>
+  <si>
+    <t>omega-3_fatty_acids</t>
+  </si>
+  <si>
+    <t>soy</t>
+  </si>
+  <si>
     <t>zinc</t>
   </si>
   <si>
-    <t>vitamin_b12</t>
-  </si>
-  <si>
-    <t>lycopene</t>
-  </si>
-  <si>
-    <t>fish_oil</t>
-  </si>
-  <si>
-    <t>caffeine</t>
-  </si>
-  <si>
-    <t>vitamin_a</t>
-  </si>
-  <si>
-    <t>phosphorus</t>
-  </si>
-  <si>
     <t>dairy</t>
   </si>
   <si>
-    <t>omega-3_fatty_acids</t>
-  </si>
-  <si>
-    <t>soy</t>
-  </si>
-  <si>
     <t>red_meat</t>
   </si>
   <si>
     <t>iron</t>
   </si>
   <si>
-    <t>copper</t>
+    <t>lactobacillus</t>
+  </si>
+  <si>
+    <t>dehydroepiandrosterone</t>
   </si>
 </sst>
 </file>
@@ -500,7 +512,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K33"/>
+  <dimension ref="A1:K37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -569,34 +581,34 @@
         <v>12</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>0.48</v>
+        <v>0.31</v>
       </c>
       <c r="D3">
-        <v>0.35</v>
+        <v>0.16</v>
       </c>
       <c r="E3">
-        <v>0.68</v>
+        <v>0.57</v>
       </c>
       <c r="F3">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="G3">
-        <v>4.3</v>
+        <v>3.94</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>64.2</v>
       </c>
       <c r="I3">
-        <v>0.6755401164826171</v>
+        <v>0.03060237178654871</v>
       </c>
       <c r="J3">
-        <v>1719</v>
+        <v>75300</v>
       </c>
       <c r="K3">
-        <v>565</v>
+        <v>667</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -604,25 +616,34 @@
         <v>13</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C4">
-        <v>0.49</v>
+        <v>0.51</v>
       </c>
       <c r="D4">
-        <v>0.32</v>
+        <v>0.4</v>
       </c>
       <c r="E4">
-        <v>0.73</v>
+        <v>0.64</v>
+      </c>
+      <c r="F4">
+        <v>0.28</v>
+      </c>
+      <c r="G4">
+        <v>0.9</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>28.9</v>
+      </c>
+      <c r="I4">
+        <v>0.4264313369285799</v>
       </c>
       <c r="J4">
-        <v>74680</v>
+        <v>4774</v>
       </c>
       <c r="K4">
-        <v>412</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -630,34 +651,25 @@
         <v>14</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C5">
-        <v>0.51</v>
+        <v>0.53</v>
       </c>
       <c r="D5">
-        <v>0.39</v>
+        <v>0.29</v>
       </c>
       <c r="E5">
-        <v>0.66</v>
-      </c>
-      <c r="F5">
-        <v>0.2</v>
-      </c>
-      <c r="G5">
-        <v>1.33</v>
+        <v>0.98</v>
       </c>
       <c r="H5">
-        <v>44.9</v>
-      </c>
-      <c r="I5">
-        <v>0.1514481902442102</v>
+        <v>41.5</v>
       </c>
       <c r="J5">
-        <v>4533</v>
+        <v>1150</v>
       </c>
       <c r="K5">
-        <v>1466</v>
+        <v>564</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -697,19 +709,19 @@
         <v>0.58</v>
       </c>
       <c r="D7">
-        <v>0.38</v>
+        <v>0.42</v>
       </c>
       <c r="E7">
-        <v>0.9</v>
+        <v>0.79</v>
       </c>
       <c r="H7">
-        <v>29.6</v>
+        <v>0</v>
       </c>
       <c r="J7">
-        <v>3144</v>
+        <v>1591</v>
       </c>
       <c r="K7">
-        <v>418</v>
+        <v>523</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -720,22 +732,22 @@
         <v>2</v>
       </c>
       <c r="C8">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="D8">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="E8">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="J8">
-        <v>1591</v>
+        <v>1592</v>
       </c>
       <c r="K8">
-        <v>523</v>
+        <v>711</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -743,25 +755,34 @@
         <v>18</v>
       </c>
       <c r="B9">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C9">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="D9">
-        <v>0.46</v>
+        <v>0.34</v>
       </c>
       <c r="E9">
-        <v>0.75</v>
+        <v>1.09</v>
+      </c>
+      <c r="F9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G9">
+        <v>5.28</v>
       </c>
       <c r="H9">
-        <v>23</v>
+        <v>90.7</v>
+      </c>
+      <c r="I9">
+        <v>0.04704275749830537</v>
       </c>
       <c r="J9">
-        <v>1592</v>
+        <v>123804</v>
       </c>
       <c r="K9">
-        <v>711</v>
+        <v>13929</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -810,19 +831,19 @@
         <v>0.65</v>
       </c>
       <c r="D11">
-        <v>0.42</v>
+        <v>0.45</v>
       </c>
       <c r="E11">
-        <v>0.98</v>
+        <v>0.93</v>
       </c>
       <c r="H11">
         <v>0</v>
       </c>
       <c r="J11">
-        <v>812</v>
+        <v>1362</v>
       </c>
       <c r="K11">
-        <v>417</v>
+        <v>454</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -830,25 +851,34 @@
         <v>21</v>
       </c>
       <c r="B12">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C12">
-        <v>0.65</v>
+        <v>0.68</v>
       </c>
       <c r="D12">
-        <v>0.45</v>
+        <v>0.53</v>
       </c>
       <c r="E12">
-        <v>0.93</v>
+        <v>0.86</v>
+      </c>
+      <c r="F12">
+        <v>0.33</v>
+      </c>
+      <c r="G12">
+        <v>1.39</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>71.7</v>
+      </c>
+      <c r="I12">
+        <v>0.0008554030642235527</v>
       </c>
       <c r="J12">
-        <v>1362</v>
+        <v>90588</v>
       </c>
       <c r="K12">
-        <v>454</v>
+        <v>9992</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -856,7 +886,7 @@
         <v>22</v>
       </c>
       <c r="B13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C13">
         <v>0.68</v>
@@ -865,16 +895,25 @@
         <v>0.44</v>
       </c>
       <c r="E13">
-        <v>1.01</v>
+        <v>1.06</v>
+      </c>
+      <c r="F13">
+        <v>0.13</v>
+      </c>
+      <c r="G13">
+        <v>3.48</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>85.2</v>
+      </c>
+      <c r="I13">
+        <v>0.05774539381341274</v>
       </c>
       <c r="J13">
-        <v>822</v>
+        <v>86259</v>
       </c>
       <c r="K13">
-        <v>424</v>
+        <v>3929</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -882,7 +921,7 @@
         <v>23</v>
       </c>
       <c r="B14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C14">
         <v>0.68</v>
@@ -891,25 +930,16 @@
         <v>0.44</v>
       </c>
       <c r="E14">
-        <v>1.06</v>
-      </c>
-      <c r="F14">
-        <v>0.13</v>
-      </c>
-      <c r="G14">
-        <v>3.48</v>
+        <v>1.01</v>
       </c>
       <c r="H14">
-        <v>85.2</v>
-      </c>
-      <c r="I14">
-        <v>0.05774539381341274</v>
+        <v>0</v>
       </c>
       <c r="J14">
-        <v>86259</v>
+        <v>822</v>
       </c>
       <c r="K14">
-        <v>3929</v>
+        <v>424</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -917,34 +947,34 @@
         <v>24</v>
       </c>
       <c r="B15">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C15">
-        <v>0.68</v>
+        <v>0.73</v>
       </c>
       <c r="D15">
-        <v>0.53</v>
+        <v>0.49</v>
       </c>
       <c r="E15">
-        <v>0.86</v>
+        <v>1.08</v>
       </c>
       <c r="F15">
-        <v>0.33</v>
+        <v>0.14</v>
       </c>
       <c r="G15">
-        <v>1.39</v>
+        <v>3.72</v>
       </c>
       <c r="H15">
-        <v>71.7</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="I15">
-        <v>0.0008554030642235527</v>
+        <v>0.0339912907502458</v>
       </c>
       <c r="J15">
-        <v>90588</v>
+        <v>4521</v>
       </c>
       <c r="K15">
-        <v>9992</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -961,16 +991,16 @@
         <v>0.57</v>
       </c>
       <c r="E16">
-        <v>1.04</v>
+        <v>1.25</v>
       </c>
       <c r="H16">
         <v>0</v>
       </c>
       <c r="J16">
-        <v>81590</v>
+        <v>443</v>
       </c>
       <c r="K16">
-        <v>8142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -987,16 +1017,16 @@
         <v>0.57</v>
       </c>
       <c r="E17">
-        <v>1.25</v>
+        <v>1.04</v>
       </c>
       <c r="H17">
         <v>0</v>
       </c>
       <c r="J17">
-        <v>443</v>
+        <v>81590</v>
       </c>
       <c r="K17">
-        <v>145</v>
+        <v>8142</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1030,34 +1060,34 @@
         <v>28</v>
       </c>
       <c r="B19">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C19">
         <v>0.78</v>
       </c>
       <c r="D19">
-        <v>0.59</v>
+        <v>0.63</v>
       </c>
       <c r="E19">
-        <v>1.04</v>
+        <v>0.97</v>
       </c>
       <c r="F19">
-        <v>0.32</v>
+        <v>0.42</v>
       </c>
       <c r="G19">
-        <v>1.91</v>
+        <v>1.45</v>
       </c>
       <c r="H19">
-        <v>72.90000000000001</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="I19">
-        <v>0.5013770685040403</v>
+        <v>0.006574139593746978</v>
       </c>
       <c r="J19">
-        <v>36197</v>
+        <v>74040</v>
       </c>
       <c r="K19">
-        <v>2521</v>
+        <v>3664</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -1065,34 +1095,34 @@
         <v>29</v>
       </c>
       <c r="B20">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C20">
-        <v>0.79</v>
+        <v>0.78</v>
       </c>
       <c r="D20">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="E20">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="F20">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="G20">
-        <v>2.01</v>
+        <v>1.91</v>
       </c>
       <c r="H20">
-        <v>56.7</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="I20">
-        <v>0.2345235869669559</v>
+        <v>0.5013770685040403</v>
       </c>
       <c r="J20">
-        <v>34075</v>
+        <v>36197</v>
       </c>
       <c r="K20">
-        <v>1876</v>
+        <v>2521</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -1100,25 +1130,34 @@
         <v>30</v>
       </c>
       <c r="B21">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C21">
-        <v>0.82</v>
+        <v>0.79</v>
       </c>
       <c r="D21">
-        <v>0.33</v>
+        <v>0.62</v>
       </c>
       <c r="E21">
-        <v>1.9</v>
+        <v>1.01</v>
+      </c>
+      <c r="F21">
+        <v>0.31</v>
+      </c>
+      <c r="G21">
+        <v>2.01</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>56.7</v>
+      </c>
+      <c r="I21">
+        <v>0.2345235869669559</v>
       </c>
       <c r="J21">
-        <v>137</v>
+        <v>34075</v>
       </c>
       <c r="K21">
-        <v>68</v>
+        <v>1876</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -1155,31 +1194,31 @@
         <v>3</v>
       </c>
       <c r="C23">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="D23">
-        <v>0.68</v>
+        <v>0.48</v>
       </c>
       <c r="E23">
-        <v>1.09</v>
+        <v>1.61</v>
       </c>
       <c r="F23">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G23">
-        <v>7.47</v>
+        <v>1689.46</v>
       </c>
       <c r="H23">
-        <v>31.4</v>
+        <v>89.5</v>
       </c>
       <c r="I23">
-        <v>0.2055380862027779</v>
+        <v>0.426317011081627</v>
       </c>
       <c r="J23">
-        <v>3463</v>
+        <v>110943</v>
       </c>
       <c r="K23">
-        <v>987</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -1187,34 +1226,34 @@
         <v>33</v>
       </c>
       <c r="B24">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C24">
         <v>0.87</v>
       </c>
       <c r="D24">
-        <v>0.48</v>
+        <v>0.34</v>
       </c>
       <c r="E24">
-        <v>1.61</v>
+        <v>2.22</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="G24">
-        <v>1689.46</v>
+        <v>52.9</v>
       </c>
       <c r="H24">
-        <v>89.5</v>
+        <v>82.3</v>
       </c>
       <c r="I24">
-        <v>0.426317011081627</v>
+        <v>0.62033124206983</v>
       </c>
       <c r="J24">
-        <v>110943</v>
+        <v>23709</v>
       </c>
       <c r="K24">
-        <v>2072</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -1222,16 +1261,16 @@
         <v>34</v>
       </c>
       <c r="B25">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C25">
         <v>0.91</v>
       </c>
       <c r="D25">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="E25">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="F25">
         <v>0.4</v>
@@ -1240,16 +1279,16 @@
         <v>2.07</v>
       </c>
       <c r="H25">
-        <v>60.8</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="I25">
-        <v>0.8631142054417383</v>
+        <v>0.8780871428365096</v>
       </c>
       <c r="J25">
-        <v>150854</v>
+        <v>26530</v>
       </c>
       <c r="K25">
-        <v>1222</v>
+        <v>7689</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -1257,16 +1296,16 @@
         <v>35</v>
       </c>
       <c r="B26">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C26">
         <v>0.91</v>
       </c>
       <c r="D26">
-        <v>0.71</v>
+        <v>0.74</v>
       </c>
       <c r="E26">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="F26">
         <v>0.4</v>
@@ -1275,16 +1314,16 @@
         <v>2.07</v>
       </c>
       <c r="H26">
-        <v>71.40000000000001</v>
+        <v>60.8</v>
       </c>
       <c r="I26">
-        <v>0.8780871428365096</v>
+        <v>0.8631142054417383</v>
       </c>
       <c r="J26">
-        <v>26530</v>
+        <v>150854</v>
       </c>
       <c r="K26">
-        <v>7689</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -1295,10 +1334,10 @@
         <v>1</v>
       </c>
       <c r="C27">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="D27">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="E27">
         <v>1</v>
@@ -1307,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="J27">
-        <v>12437</v>
+        <v>1706</v>
       </c>
       <c r="K27">
-        <v>386</v>
+        <v>853</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -1318,34 +1357,25 @@
         <v>37</v>
       </c>
       <c r="B28">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C28">
-        <v>1.06</v>
+        <v>0.99</v>
       </c>
       <c r="D28">
-        <v>0.5600000000000001</v>
+        <v>0.88</v>
       </c>
       <c r="E28">
-        <v>2.02</v>
-      </c>
-      <c r="F28">
-        <v>0.1</v>
-      </c>
-      <c r="G28">
-        <v>11.32</v>
+        <v>1.12</v>
       </c>
       <c r="H28">
-        <v>98.5</v>
-      </c>
-      <c r="I28">
-        <v>0.9286238558326152</v>
+        <v>0</v>
       </c>
       <c r="J28">
-        <v>177825</v>
+        <v>121885</v>
       </c>
       <c r="K28">
-        <v>18523</v>
+        <v>12906</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -1353,34 +1383,25 @@
         <v>38</v>
       </c>
       <c r="B29">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C29">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="D29">
-        <v>0.66</v>
+        <v>1</v>
       </c>
       <c r="E29">
-        <v>1.91</v>
-      </c>
-      <c r="F29">
-        <v>0.17</v>
-      </c>
-      <c r="G29">
-        <v>7.68</v>
+        <v>1</v>
       </c>
       <c r="H29">
-        <v>97.8</v>
-      </c>
-      <c r="I29">
-        <v>0.7232591647058118</v>
+        <v>0</v>
       </c>
       <c r="J29">
-        <v>471078</v>
+        <v>12437</v>
       </c>
       <c r="K29">
-        <v>7212</v>
+        <v>386</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -1388,34 +1409,34 @@
         <v>39</v>
       </c>
       <c r="B30">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C30">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="D30">
-        <v>0.76</v>
+        <v>0.66</v>
       </c>
       <c r="E30">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="F30">
-        <v>0.23</v>
+        <v>0.17</v>
       </c>
       <c r="G30">
-        <v>6.08</v>
+        <v>7.68</v>
       </c>
       <c r="H30">
-        <v>97.5</v>
+        <v>97.8</v>
       </c>
       <c r="I30">
-        <v>0.9295959990787233</v>
+        <v>0.7232591647058118</v>
       </c>
       <c r="J30">
-        <v>151854</v>
+        <v>471078</v>
       </c>
       <c r="K30">
-        <v>3291</v>
+        <v>7212</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -1423,34 +1444,34 @@
         <v>40</v>
       </c>
       <c r="B31">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C31">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
       <c r="D31">
-        <v>1.17</v>
+        <v>0.76</v>
       </c>
       <c r="E31">
-        <v>1.66</v>
+        <v>1.83</v>
       </c>
       <c r="F31">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="G31">
-        <v>7.81</v>
+        <v>6.08</v>
       </c>
       <c r="H31">
-        <v>46.2</v>
+        <v>97.5</v>
       </c>
       <c r="I31">
-        <v>0.7146765353733536</v>
+        <v>0.9295959990787233</v>
       </c>
       <c r="J31">
-        <v>41569</v>
+        <v>151854</v>
       </c>
       <c r="K31">
-        <v>1404</v>
+        <v>3291</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -1458,34 +1479,25 @@
         <v>41</v>
       </c>
       <c r="B32">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C32">
-        <v>1.47</v>
+        <v>1.21</v>
       </c>
       <c r="D32">
-        <v>1.23</v>
+        <v>0.99</v>
       </c>
       <c r="E32">
-        <v>1.77</v>
-      </c>
-      <c r="F32">
-        <v>0.32</v>
-      </c>
-      <c r="G32">
-        <v>6.72</v>
+        <v>1.48</v>
       </c>
       <c r="H32">
-        <v>21.1</v>
-      </c>
-      <c r="I32">
-        <v>0.7203820715741027</v>
+        <v>0</v>
       </c>
       <c r="J32">
-        <v>66907</v>
+        <v>61032</v>
       </c>
       <c r="K32">
-        <v>2633</v>
+        <v>788</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -1493,25 +1505,165 @@
         <v>42</v>
       </c>
       <c r="B33">
+        <v>7</v>
+      </c>
+      <c r="C33">
+        <v>1.21</v>
+      </c>
+      <c r="D33">
+        <v>0.67</v>
+      </c>
+      <c r="E33">
+        <v>2.2</v>
+      </c>
+      <c r="F33">
+        <v>0.14</v>
+      </c>
+      <c r="G33">
+        <v>10.52</v>
+      </c>
+      <c r="H33">
+        <v>98.3</v>
+      </c>
+      <c r="I33">
+        <v>0.7984491065727577</v>
+      </c>
+      <c r="J33">
+        <v>433021</v>
+      </c>
+      <c r="K33">
+        <v>26434</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11">
+      <c r="A34" t="s">
+        <v>43</v>
+      </c>
+      <c r="B34">
+        <v>3</v>
+      </c>
+      <c r="C34">
+        <v>1.4</v>
+      </c>
+      <c r="D34">
+        <v>1.17</v>
+      </c>
+      <c r="E34">
+        <v>1.66</v>
+      </c>
+      <c r="F34">
+        <v>0.25</v>
+      </c>
+      <c r="G34">
+        <v>7.81</v>
+      </c>
+      <c r="H34">
+        <v>46.2</v>
+      </c>
+      <c r="I34">
+        <v>0.7146765353733536</v>
+      </c>
+      <c r="J34">
+        <v>41569</v>
+      </c>
+      <c r="K34">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11">
+      <c r="A35" t="s">
+        <v>44</v>
+      </c>
+      <c r="B35">
+        <v>4</v>
+      </c>
+      <c r="C35">
+        <v>1.47</v>
+      </c>
+      <c r="D35">
+        <v>1.28</v>
+      </c>
+      <c r="E35">
+        <v>1.69</v>
+      </c>
+      <c r="F35">
+        <v>1.08</v>
+      </c>
+      <c r="G35">
+        <v>2.01</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35">
+        <v>0.5692336538290566</v>
+      </c>
+      <c r="J35">
+        <v>72387</v>
+      </c>
+      <c r="K35">
+        <v>2803</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11">
+      <c r="A36" t="s">
+        <v>45</v>
+      </c>
+      <c r="B36">
+        <v>3</v>
+      </c>
+      <c r="C36">
+        <v>1.59</v>
+      </c>
+      <c r="D36">
+        <v>0.45</v>
+      </c>
+      <c r="E36">
+        <v>5.63</v>
+      </c>
+      <c r="F36">
+        <v>0</v>
+      </c>
+      <c r="G36">
+        <v>11519830.38</v>
+      </c>
+      <c r="H36">
+        <v>90.5</v>
+      </c>
+      <c r="I36">
+        <v>0.02912942499259806</v>
+      </c>
+      <c r="J36">
+        <v>750</v>
+      </c>
+      <c r="K36">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11">
+      <c r="A37" t="s">
+        <v>46</v>
+      </c>
+      <c r="B37">
         <v>1</v>
       </c>
-      <c r="C33">
-        <v>2.24</v>
-      </c>
-      <c r="D33">
-        <v>1.26</v>
-      </c>
-      <c r="E33">
-        <v>3.56</v>
-      </c>
-      <c r="H33">
-        <v>0</v>
-      </c>
-      <c r="J33">
-        <v>12437</v>
-      </c>
-      <c r="K33">
-        <v>386</v>
+      <c r="C37">
+        <v>1.67</v>
+      </c>
+      <c r="D37">
+        <v>1.05</v>
+      </c>
+      <c r="E37">
+        <v>2.51</v>
+      </c>
+      <c r="H37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>667</v>
+      </c>
+      <c r="K37">
+        <v>313</v>
       </c>
     </row>
   </sheetData>

--- a/exposures_meta_analysis_uterine_combined.xlsx
+++ b/exposures_meta_analysis_uterine_combined.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,57 +429,57 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Exposure</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>number studies</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Pooled RR</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>lower CI RR</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>upper CI RR</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>lower PI RR</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>upper PI RR</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>I^2 (%)</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eggers p-value</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>total N</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>total Cases</t>
         </is>
@@ -532,7 +544,7 @@
         <v>64.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.03060237178654872</v>
+        <v>0.03060237178654871</v>
       </c>
       <c r="J3" t="n">
         <v>75300</v>
@@ -569,7 +581,7 @@
         <v>28.9</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4264313369285802</v>
+        <v>0.4264313369285799</v>
       </c>
       <c r="J4" t="n">
         <v>4774</v>
@@ -730,7 +742,7 @@
         <v>90.7</v>
       </c>
       <c r="I9" t="n">
-        <v>0.04704275749830538</v>
+        <v>0.04704275749830537</v>
       </c>
       <c r="J9" t="n">
         <v>123804</v>
@@ -767,7 +779,7 @@
         <v>93.09999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>0.484788327891376</v>
+        <v>0.4847883278913757</v>
       </c>
       <c r="J10" t="n">
         <v>90098</v>
@@ -810,85 +822,79 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>calcium</t>
+          <t>quercetin</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C12" t="n">
         <v>0.68</v>
       </c>
       <c r="D12" t="n">
-        <v>0.53</v>
+        <v>0.44</v>
       </c>
       <c r="E12" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="G12" t="n">
-        <v>1.39</v>
-      </c>
+        <v>1.01</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>71.7</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0.0008554030642235538</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="n">
-        <v>90588</v>
+        <v>822</v>
       </c>
       <c r="K12" t="n">
-        <v>9992</v>
+        <v>424</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>beta-carotene</t>
+          <t>calcium</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
         <v>0.68</v>
       </c>
       <c r="D13" t="n">
-        <v>0.44</v>
+        <v>0.53</v>
       </c>
       <c r="E13" t="n">
-        <v>1.06</v>
+        <v>0.86</v>
       </c>
       <c r="F13" t="n">
-        <v>0.13</v>
+        <v>0.33</v>
       </c>
       <c r="G13" t="n">
-        <v>3.48</v>
+        <v>1.39</v>
       </c>
       <c r="H13" t="n">
-        <v>85.2</v>
+        <v>71.7</v>
       </c>
       <c r="I13" t="n">
-        <v>0.05774539381341278</v>
+        <v>0.0008554030642235527</v>
       </c>
       <c r="J13" t="n">
-        <v>86259</v>
+        <v>90588</v>
       </c>
       <c r="K13" t="n">
-        <v>3929</v>
+        <v>9992</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>quercetin</t>
+          <t>beta-carotene</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
         <v>0.68</v>
@@ -897,19 +903,25 @@
         <v>0.44</v>
       </c>
       <c r="E14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
+        <v>1.06</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="G14" t="n">
+        <v>3.48</v>
+      </c>
       <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="inlineStr"/>
+        <v>85.2</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.05774539381341274</v>
+      </c>
       <c r="J14" t="n">
-        <v>822</v>
+        <v>86259</v>
       </c>
       <c r="K14" t="n">
-        <v>424</v>
+        <v>3929</v>
       </c>
     </row>
     <row r="15">
@@ -940,7 +952,7 @@
         <v>70.59999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>0.03399129075024581</v>
+        <v>0.0339912907502458</v>
       </c>
       <c r="J15" t="n">
         <v>4521</v>
@@ -952,7 +964,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>olive</t>
+          <t>fermented_foods</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -965,7 +977,7 @@
         <v>0.57</v>
       </c>
       <c r="E16" t="n">
-        <v>1.25</v>
+        <v>1.04</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
@@ -974,16 +986,16 @@
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="n">
-        <v>443</v>
+        <v>81590</v>
       </c>
       <c r="K16" t="n">
-        <v>145</v>
+        <v>8142</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>non-alcoholic_fermented_foods</t>
+          <t>olive</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -996,7 +1008,7 @@
         <v>0.57</v>
       </c>
       <c r="E17" t="n">
-        <v>1.04</v>
+        <v>1.25</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
@@ -1005,10 +1017,10 @@
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="n">
-        <v>81590</v>
+        <v>443</v>
       </c>
       <c r="K17" t="n">
-        <v>8142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="18">
@@ -1070,7 +1082,7 @@
         <v>64.09999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>0.006574139593746981</v>
+        <v>0.006574139593746978</v>
       </c>
       <c r="J19" t="n">
         <v>74040</v>
@@ -1107,7 +1119,7 @@
         <v>72.90000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>0.50137706850404</v>
+        <v>0.5013770685040403</v>
       </c>
       <c r="J20" t="n">
         <v>36197</v>
@@ -1144,7 +1156,7 @@
         <v>56.7</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2345235869669558</v>
+        <v>0.2345235869669559</v>
       </c>
       <c r="J21" t="n">
         <v>34075</v>
@@ -1212,7 +1224,7 @@
         <v>89.5</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4263170110816271</v>
+        <v>0.426317011081627</v>
       </c>
       <c r="J23" t="n">
         <v>110943</v>
@@ -1249,7 +1261,7 @@
         <v>82.3</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6203312420698301</v>
+        <v>0.62033124206983</v>
       </c>
       <c r="J24" t="n">
         <v>23709</v>
@@ -1558,7 +1570,7 @@
         <v>98.3</v>
       </c>
       <c r="I33" t="n">
-        <v>0.7984491065727578</v>
+        <v>0.7984491065727577</v>
       </c>
       <c r="J33" t="n">
         <v>433021</v>
@@ -1595,7 +1607,7 @@
         <v>46.2</v>
       </c>
       <c r="I34" t="n">
-        <v>0.7146765353733535</v>
+        <v>0.7146765353733536</v>
       </c>
       <c r="J34" t="n">
         <v>41569</v>
@@ -1669,7 +1681,7 @@
         <v>90.5</v>
       </c>
       <c r="I36" t="n">
-        <v>0.02912942499259846</v>
+        <v>0.02912942499259806</v>
       </c>
       <c r="J36" t="n">
         <v>750</v>
